--- a/data/trans_orig/P24E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007 (tasa de respuesta: 98,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43180</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>57084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26935</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43172</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27646</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35089</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>53956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>19407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33745</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>34400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51679</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>66276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23986</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>42230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71797</t>
+          <t>72632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101473</t>
+          <t>101990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>76404</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101451</t>
+          <t>101529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56988</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121431</t>
+          <t>120374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152835</t>
+          <t>151354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>31889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>32712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45744</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67142</t>
+          <t>68535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114785</t>
+          <t>114172</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>154000</t>
+          <t>152665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>216203</t>
+          <t>218714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>267613</t>
+          <t>270017</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>196981</t>
+          <t>197846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>236889</t>
+          <t>239208</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>336118</t>
+          <t>334307</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>387431</t>
+          <t>387820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73061</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>82377</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>118897</t>
+          <t>117856</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>68927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53007</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77972</t>
+          <t>76533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>25494</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47999</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73966</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>57887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84625</t>
+          <t>84567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45342</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>64191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>49036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73591</t>
+          <t>73387</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60956</t>
+          <t>62886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90059</t>
+          <t>90827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36867</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60002</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>88265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75852</t>
+          <t>76414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119908</t>
+          <t>118310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157259</t>
+          <t>155222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103206</t>
+          <t>103159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135979</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>48979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73135</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157237</t>
+          <t>162139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>199642</t>
+          <t>202224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77231</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>45749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73634</t>
+          <t>74370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101851</t>
+          <t>101776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>40214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>38031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61150</t>
+          <t>59407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>66812</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95154</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>49439</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20612</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>266205</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201680</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>246549</t>
+          <t>246045</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>429150</t>
+          <t>428935</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>497431</t>
+          <t>497483</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>271644</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>325231</t>
+          <t>325611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>180332</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>226940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>466350</t>
+          <t>463343</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>534788</t>
+          <t>534896</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>102087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016 (tasa de respuesta: 98,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>38572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44947</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65486</t>
+          <t>64904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33940</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>41696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52563</t>
+          <t>52778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>90112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60607</t>
+          <t>58864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>41018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62343</t>
+          <t>62992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81739</t>
+          <t>80923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114901</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81513</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109365</t>
+          <t>109335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>51959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74949</t>
+          <t>75198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143568</t>
+          <t>143025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179814</t>
+          <t>179413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27661</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35629</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78257</t>
+          <t>79286</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>36651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40746</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59333</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39139</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58200</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84825</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112266</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24274</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39035</t>
+          <t>40029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45350</t>
+          <t>45702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111462</t>
+          <t>110350</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149796</t>
+          <t>150773</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228057</t>
+          <t>228211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282432</t>
+          <t>285476</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>251844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>295072</t>
+          <t>297472</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188023</t>
+          <t>188183</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>229106</t>
+          <t>228262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>449718</t>
+          <t>448834</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>510068</t>
+          <t>508867</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>76557</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>139515</t>
+          <t>138476</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>185314</t>
+          <t>185724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24E-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46345</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44296</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57084</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53956</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>41241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>52032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>40861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42618</t>
+          <t>42250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66276</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72632</t>
+          <t>72013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101990</t>
+          <t>102447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76404</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>101124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57049</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120374</t>
+          <t>122437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151354</t>
+          <t>153734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38329</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>43691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24282</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>39300</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>45692</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68535</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31881</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>33626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114172</t>
+          <t>115512</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>152665</t>
+          <t>151731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>218714</t>
+          <t>216390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>270017</t>
+          <t>266481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>197846</t>
+          <t>196344</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>239208</t>
+          <t>236635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>334307</t>
+          <t>335668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>387820</t>
+          <t>387448</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>44730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>71739</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82377</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117856</t>
+          <t>120364</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40064</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>34640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>46172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68927</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>34332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>52358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76533</t>
+          <t>75243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>21753</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44825</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47793</t>
+          <t>48700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73579</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>43030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>85448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12448</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>46077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64191</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>91934</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49036</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73387</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62886</t>
+          <t>62115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90827</t>
+          <t>89395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34959</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88265</t>
+          <t>88832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76414</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118310</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>157481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103159</t>
+          <t>102297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134798</t>
+          <t>134660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>72645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162139</t>
+          <t>159724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202224</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>50301</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77559</t>
+          <t>77345</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>45584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>40384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62921</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74370</t>
+          <t>74396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101776</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40214</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38031</t>
+          <t>37941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66812</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94909</t>
+          <t>95035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>42282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37244</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265488</t>
+          <t>264725</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>246045</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>428935</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>497483</t>
+          <t>495545</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>273722</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>325611</t>
+          <t>326506</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>463343</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>534896</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>101872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>173376</t>
+          <t>171650</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44880</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64904</t>
+          <t>64984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>58983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41696</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52778</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72667</t>
+          <t>73023</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67613</t>
+          <t>67792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90112</t>
+          <t>91020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58864</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41018</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62992</t>
+          <t>62364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80923</t>
+          <t>81430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114157</t>
+          <t>114054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81339</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109335</t>
+          <t>110558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75198</t>
+          <t>74970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143025</t>
+          <t>144779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179413</t>
+          <t>180261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28333</t>
+          <t>26947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50674</t>
+          <t>50241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49627</t>
+          <t>49221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79286</t>
+          <t>76738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36651</t>
+          <t>37750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37795</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>39508</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>58567</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40362</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85291</t>
+          <t>84266</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>110646</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40029</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27442</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>44902</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>111725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>150773</t>
+          <t>153416</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>144340</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228211</t>
+          <t>228896</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>285476</t>
+          <t>281796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>251844</t>
+          <t>247394</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>297472</t>
+          <t>294895</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188183</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>228262</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>448834</t>
+          <t>451475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>508867</t>
+          <t>508500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78724</t>
+          <t>76734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113604</t>
+          <t>113889</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>138476</t>
+          <t>139372</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>185724</t>
+          <t>186475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
